--- a/generator/WY_Mining_Ops_Simulator.xlsx
+++ b/generator/WY_Mining_Ops_Simulator.xlsx
@@ -2066,7 +2066,7 @@
         <f>SEQUENCE(DaysCount)</f>
         <v/>
       </c>
-      <c r="B3">
+      <c r="B3" s="22">
         <f>SEQUENCE(DaysCount,1,StartDate,1)</f>
         <v/>
       </c>
